--- a/volunteer_forms/033_summer_camp_volunteer_questionnaire--volunteer_forms.xlsx
+++ b/volunteer_forms/033_summer_camp_volunteer_questionnaire--volunteer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,8 +854,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Text Message'}</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'summer_camps'}</t>
+          <t>summer_camps</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Summer Camps'}</t>
+          <t>Summer Camps</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'camp_counselor'}</t>
+          <t>camp_counselor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Camp Counselor'}</t>
+          <t>Camp Counselor</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'group_leader'}</t>
+          <t>group_leader</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Group Leader'}</t>
+          <t>Group Leader</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'bike'}</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Bike'}</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'medical_condition_1'}</t>
+          <t>medical_condition_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Medical Condition 1'}</t>
+          <t>Medical Condition 1</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'medical_condition_2'}</t>
+          <t>medical_condition_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Medical Condition 2'}</t>
+          <t>Medical Condition 2</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'first_aid'}</t>
+          <t>first_aid</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'First Aid'}</t>
+          <t>First Aid</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'cpr'}</t>
+          <t>cpr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'CPR'}</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'epipen'}</t>
+          <t>epipen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'EpiPen'}</t>
+          <t>EpiPen</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'name1'}</t>
+          <t>name1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Name1'}</t>
+          <t>Name1</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'name2'}</t>
+          <t>name2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Name2'}</t>
+          <t>Name2</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'name3'}</t>
+          <t>name3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Name3'}</t>
+          <t>Name3</t>
         </is>
       </c>
     </row>
